--- a/UnUn-Transmatch.xlsx
+++ b/UnUn-Transmatch.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="UnUn Calculator" sheetId="1" state="visible" r:id="rId3"/>
@@ -4022,7 +4022,7 @@
         <v>95</v>
       </c>
       <c r="C9" s="52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" s="53" t="s">
         <v>96</v>
@@ -4238,7 +4238,7 @@
         <v>-12</v>
       </c>
       <c r="F15" s="59" t="str">
-        <f aca="false">IF(ROW()-15&lt;=$C$9,"YES","NO")</f>
+        <f aca="false">IF(ROW()-14&lt;=$C$9,"YES","NO")</f>
         <v>YES</v>
       </c>
       <c r="G15" s="62"/>
@@ -4278,7 +4278,7 @@
         <v>23</v>
       </c>
       <c r="F16" s="59" t="str">
-        <f aca="false">IF(ROW()-15&lt;=$C$9,"YES","NO")</f>
+        <f aca="false">IF(ROW()-14&lt;=$C$9,"YES","NO")</f>
         <v>YES</v>
       </c>
       <c r="G16" s="62"/>
@@ -4318,7 +4318,7 @@
         <v>10</v>
       </c>
       <c r="F17" s="59" t="str">
-        <f aca="false">IF(ROW()-15&lt;=$C$9,"YES","NO")</f>
+        <f aca="false">IF(ROW()-14&lt;=$C$9,"YES","NO")</f>
         <v>YES</v>
       </c>
       <c r="G17" s="62"/>
@@ -4352,7 +4352,7 @@
       <c r="D18" s="60"/>
       <c r="E18" s="61"/>
       <c r="F18" s="59" t="str">
-        <f aca="false">IF(ROW()-15&lt;=$C$9,"YES","NO")</f>
+        <f aca="false">IF(ROW()-14&lt;=$C$9,"YES","NO")</f>
         <v>NO</v>
       </c>
       <c r="G18" s="62"/>
@@ -4386,7 +4386,7 @@
       <c r="D19" s="60"/>
       <c r="E19" s="61"/>
       <c r="F19" s="59" t="str">
-        <f aca="false">IF(ROW()-15&lt;=$C$9,"YES","NO")</f>
+        <f aca="false">IF(ROW()-14&lt;=$C$9,"YES","NO")</f>
         <v>NO</v>
       </c>
       <c r="G19" s="62"/>
@@ -4420,7 +4420,7 @@
       <c r="D20" s="60"/>
       <c r="E20" s="61"/>
       <c r="F20" s="59" t="str">
-        <f aca="false">IF(ROW()-15&lt;=$C$9,"YES","NO")</f>
+        <f aca="false">IF(ROW()-14&lt;=$C$9,"YES","NO")</f>
         <v>NO</v>
       </c>
       <c r="G20" s="62"/>
@@ -4454,7 +4454,7 @@
       <c r="D21" s="60"/>
       <c r="E21" s="61"/>
       <c r="F21" s="59" t="str">
-        <f aca="false">IF(ROW()-15&lt;=$C$9,"YES","NO")</f>
+        <f aca="false">IF(ROW()-14&lt;=$C$9,"YES","NO")</f>
         <v>NO</v>
       </c>
       <c r="G21" s="62"/>
@@ -4488,7 +4488,7 @@
       <c r="D22" s="60"/>
       <c r="E22" s="61"/>
       <c r="F22" s="59" t="str">
-        <f aca="false">IF(ROW()-15&lt;=$C$9,"YES","NO")</f>
+        <f aca="false">IF(ROW()-14&lt;=$C$9,"YES","NO")</f>
         <v>NO</v>
       </c>
       <c r="G22" s="62"/>
@@ -4522,7 +4522,7 @@
       <c r="D23" s="60"/>
       <c r="E23" s="61"/>
       <c r="F23" s="59" t="str">
-        <f aca="false">IF(ROW()-15&lt;=$C$9,"YES","NO")</f>
+        <f aca="false">IF(ROW()-14&lt;=$C$9,"YES","NO")</f>
         <v>NO</v>
       </c>
       <c r="G23" s="62"/>
@@ -4556,7 +4556,7 @@
       <c r="D24" s="60"/>
       <c r="E24" s="61"/>
       <c r="F24" s="59" t="str">
-        <f aca="false">IF(ROW()-15&lt;=$C$9,"YES","NO")</f>
+        <f aca="false">IF(ROW()-14&lt;=$C$9,"YES","NO")</f>
         <v>NO</v>
       </c>
       <c r="G24" s="62"/>
@@ -4590,7 +4590,7 @@
       <c r="D25" s="60"/>
       <c r="E25" s="61"/>
       <c r="F25" s="59" t="str">
-        <f aca="false">IF(ROW()-15&lt;=$C$9,"YES","NO")</f>
+        <f aca="false">IF(ROW()-14&lt;=$C$9,"YES","NO")</f>
         <v>NO</v>
       </c>
       <c r="G25" s="62"/>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="C34" s="53" t="n">
         <f aca="false">C9</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D34" s="65" t="s">
         <v>96</v>

--- a/UnUn-Transmatch.xlsx
+++ b/UnUn-Transmatch.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="UnUn Calculator" sheetId="1" state="visible" r:id="rId3"/>
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Operating Frequency</t>
   </si>
   <si>
-    <t xml:space="preserve">MHz  [auto ↑]</t>
+    <t xml:space="preserve">MHz</t>
   </si>
   <si>
     <t xml:space="preserve">Target Input Impedance (Real, Rin)</t>
@@ -1886,7 +1886,6 @@
         <v>3</v>
       </c>
       <c r="C5" s="8" t="n">
-        <f aca="false">IFERROR(INDEX(#REF!,MATCH(#REF!,#REF!,0)),7.1)</f>
         <v>7.1</v>
       </c>
       <c r="D5" s="9" t="s">
